--- a/artfynd/A 3916-2025 artfynd.xlsx
+++ b/artfynd/A 3916-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63200558</v>
+        <v>135161250</v>
       </c>
       <c r="B2" t="n">
-        <v>56830</v>
+        <v>57912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,61 +686,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>100082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljungbyholm, Sm</t>
+          <t>Österlundagärdena, Österlundagärdena, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565825</v>
+        <v>565828</v>
       </c>
       <c r="R2" t="n">
-        <v>6278192</v>
+        <v>6278331</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,17 +756,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-06-04</t>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>lokal-ID: 13  Box-ID: 14E</t>
+          <t>Förbiflygande, cirklade ett tag och drog NV.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +791,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63202846</v>
+        <v>63200558</v>
       </c>
       <c r="B3" t="n">
-        <v>56835</v>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,26 +814,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -927,37 +929,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63189070</v>
+        <v>63202846</v>
       </c>
       <c r="B4" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1053,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63228787</v>
+        <v>63189070</v>
       </c>
       <c r="B5" t="n">
-        <v>56837</v>
+        <v>56816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,26 +1066,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1176,6 +1178,132 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>63228787</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ljungbyholm, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565825</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6278192</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-06-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-06-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>lokal-ID: 13  Box-ID: 14E</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3916-2025 artfynd.xlsx
+++ b/artfynd/A 3916-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135161250</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63200558</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63202846</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1178,6 +1198,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189070</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1304,8 +1329,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63228787</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 3916-2025 artfynd.xlsx
+++ b/artfynd/A 3916-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135161250</v>
       </c>
       <c r="B2" t="n">
-        <v>57912</v>
+        <v>57917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
